--- a/marketing/recipients.template.xlsx
+++ b/marketing/recipients.template.xlsx
@@ -397,12 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,32 +409,357 @@
       <c r="C1" t="str">
         <v>name</v>
       </c>
+      <c r="D1" t="str">
+        <v>sent</v>
+      </c>
+      <c r="E1" t="str">
+        <v>__EMPTY</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>contact@example.com</v>
+        <v>abedaarabi@gmail.com</v>
       </c>
       <c r="B2" t="str">
-        <v>Acme Construction</v>
+        <v>Abed and co</v>
       </c>
       <c r="C2" t="str">
-        <v>Alex</v>
+        <v>Abed</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ops@example.org</v>
+        <v>info@kadcon.com</v>
       </c>
       <c r="B3" t="str">
-        <v>BuildCo FM</v>
+        <v>KADCON Corp</v>
       </c>
       <c r="C3" t="str">
+        <v>KADCON Corp</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>info@pcsgc.com</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Potomac Construction</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Potomac Construction</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>info@martoneconstruction.com</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Martone Construction</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Martone Construction</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str" xml:space="preserve">
+        <v xml:space="preserve">info@hrconstruction.com
+</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Martone Construction</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Martone Construction</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>jdoe@corenic-cg.com</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Corenic Construction</v>
+      </c>
+      <c r="C7" t="str">
+        <v>James Morrow</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>info@midatlanticgc.com</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Mid-Atlantic General</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Mid-Atlantic General</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>firstname@hrgm.com</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HRGM Corporation</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>x@avsmoot.com</v>
+      </c>
+      <c r="B10" t="str">
+        <v>AVSmoot LLC</v>
+      </c>
+      <c r="C10" t="str">
+        <v>AVSmoot LLC</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>info@wcsconstruction.com</v>
+      </c>
+      <c r="B11" t="str">
+        <v>WCS Construction</v>
+      </c>
+      <c r="C11" t="str">
+        <v>WCS Construction</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>janed@trinitygc.us</v>
+      </c>
+      <c r="B12" t="str">
+        <v>TRINITY Group</v>
+      </c>
+      <c r="C12" t="str">
+        <v>TRINITY Group</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>jbecker@trinitygc.us</v>
+      </c>
+      <c r="B13" t="str">
+        <v>TRINITY Group</v>
+      </c>
+      <c r="C13" t="str">
+        <v xml:space="preserve"> Janelle Becker </v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>firstname@buch.us.com</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Buch Construction</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Buch Construction</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>jcorona@buch.us.com</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Buch Construction</v>
+      </c>
+      <c r="C15" t="str">
+        <v xml:space="preserve">Julia Corona </v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v xml:space="preserve">doe@randcc.com </v>
+      </c>
+      <c r="B16" t="str">
+        <v>rand construction</v>
+      </c>
+      <c r="C16" t="str">
+        <v>rand construction</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>mkillelea@lfjennings.com</v>
+      </c>
+      <c r="B17" t="str">
+        <v>L.F. Jennings</v>
+      </c>
+      <c r="C17" t="str">
+        <v xml:space="preserve">Mike Killelea </v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>firstname@holladayconstruction.com</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Holladay Construction</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Holladay Construction</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>simondevelopmentcorp.com</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Simon Development &amp; Construction</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Simon Development &amp; Construction</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>aidintd@gmail.com</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Aidintd</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Aidintd</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>mail@art-tek.dk</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Art-Tek</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Rodein</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E21"/>
   </ignoredErrors>
 </worksheet>
 </file>